--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hrproject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9768B425-3AFF-41F1-92B7-CC5B2125C2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C8C4B3-5276-433D-90D5-0D29A3158970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{63DA0A74-B8C9-4ECD-9CA8-5CD4D1273B96}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="203">
   <si>
     <t>บริษัท คอมพลีท โอโต รับเบอร์ แมนูแฟ็คเจอริ่ง จำกัด</t>
   </si>
@@ -495,9 +495,6 @@
   </si>
   <si>
     <t>หมายเหตุ :  หากมีข้อมูลเพิ่มโปรดเพิ่ม Sheet แนบ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตัวอย่าง E-Memo (ปัจจุบัน) ทำใส่ไฟล์เอกสาร Excel </t>
   </si>
   <si>
     <r>
@@ -2234,29 +2231,29 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="E2" s="41" t="s">
         <v>143</v>
-      </c>
-      <c r="E2" s="41" t="s">
-        <v>144</v>
       </c>
       <c r="F2" s="42"/>
       <c r="G2" s="43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H2" s="44"/>
       <c r="I2" s="45"/>
@@ -2269,13 +2266,13 @@
       <c r="E3" s="49"/>
       <c r="F3" s="50"/>
       <c r="G3" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="I3" s="51" t="s">
         <v>147</v>
-      </c>
-      <c r="I3" s="51" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2283,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C4" s="54"/>
       <c r="D4" s="54"/>
@@ -2291,7 +2288,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" s="57"/>
       <c r="H4" s="58"/>
@@ -2300,26 +2297,26 @@
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59"/>
       <c r="B5" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="D5" s="62" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="62" t="s">
-        <v>153</v>
       </c>
       <c r="E5" s="63"/>
       <c r="F5" s="64"/>
       <c r="G5" s="65"/>
       <c r="H5" s="66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I5" s="65"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59"/>
       <c r="B6" s="60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="68"/>
@@ -2332,22 +2329,22 @@
     <row r="7" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59"/>
       <c r="B7" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="D7" s="74" t="s">
         <v>157</v>
-      </c>
-      <c r="D7" s="74" t="s">
-        <v>158</v>
       </c>
       <c r="E7" s="75">
         <v>1.2</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G7" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7" s="78"/>
       <c r="I7" s="78"/>
@@ -2355,28 +2352,28 @@
     <row r="8" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59"/>
       <c r="B8" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="66" t="s">
         <v>160</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>161</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="80">
         <v>1.3</v>
       </c>
       <c r="F8" s="81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G8" s="82"/>
       <c r="H8" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I8" s="82"/>
     </row>
     <row r="9" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59"/>
       <c r="B9" s="60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" s="84"/>
       <c r="D9" s="79"/>
@@ -2384,32 +2381,32 @@
         <v>1.4</v>
       </c>
       <c r="F9" s="86" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G9" s="87"/>
       <c r="H9" s="87"/>
       <c r="I9" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59"/>
       <c r="B10" s="60"/>
       <c r="C10" s="89" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="90" t="s">
         <v>165</v>
-      </c>
-      <c r="D10" s="90" t="s">
-        <v>166</v>
       </c>
       <c r="E10" s="91">
         <v>1.5</v>
       </c>
       <c r="F10" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="73"/>
       <c r="H10" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I10" s="73"/>
     </row>
@@ -2417,14 +2414,14 @@
       <c r="A11" s="59"/>
       <c r="B11" s="60"/>
       <c r="C11" s="89" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="92" t="s">
         <v>168</v>
-      </c>
-      <c r="D11" s="92" t="s">
-        <v>169</v>
       </c>
       <c r="E11" s="93"/>
       <c r="F11" s="66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G11" s="94"/>
       <c r="H11" s="94"/>
@@ -2439,12 +2436,12 @@
         <v>1.6</v>
       </c>
       <c r="F12" s="95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G12" s="87"/>
       <c r="H12" s="87"/>
       <c r="I12" s="96" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -2452,7 +2449,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C13" s="98"/>
       <c r="D13" s="90"/>
@@ -2465,86 +2462,86 @@
     <row r="14" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="59"/>
       <c r="B14" s="103" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="80">
         <v>2.1</v>
       </c>
       <c r="F14" s="104" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G14" s="105"/>
       <c r="H14" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I14" s="82"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="59"/>
       <c r="B15" s="103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D15" s="106" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" s="107">
         <v>2.2000000000000002</v>
       </c>
       <c r="F15" s="108" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G15" s="109"/>
       <c r="H15" s="87"/>
       <c r="I15" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="59"/>
       <c r="B16" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="110" t="s">
         <v>177</v>
       </c>
-      <c r="C16" s="110" t="s">
-        <v>178</v>
-      </c>
       <c r="D16" s="92" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" s="111">
         <v>2.2999999999999998</v>
       </c>
       <c r="F16" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G16" s="73"/>
       <c r="H16" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I16" s="73"/>
     </row>
     <row r="17" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="59"/>
       <c r="B17" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="89" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="89" t="s">
-        <v>180</v>
-      </c>
       <c r="D17" s="92" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E17" s="112"/>
       <c r="F17" s="66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G17" s="94"/>
       <c r="H17" s="94"/>
@@ -2553,7 +2550,7 @@
     <row r="18" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="113"/>
       <c r="B18" s="60" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="89"/>
       <c r="D18" s="92"/>
@@ -2561,12 +2558,12 @@
         <v>2.4</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G18" s="88"/>
       <c r="H18" s="88"/>
       <c r="I18" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2574,7 +2571,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="116" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C19" s="54"/>
       <c r="D19" s="117"/>
@@ -2588,20 +2585,20 @@
     <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="123"/>
       <c r="B20" s="124" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C20" s="125" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D20" s="126"/>
       <c r="E20" s="127">
         <v>3.1</v>
       </c>
       <c r="F20" s="128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G20" s="129" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H20" s="129"/>
       <c r="I20" s="130"/>
@@ -2609,28 +2606,28 @@
     <row r="21" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="123"/>
       <c r="B21" s="124" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D21" s="126"/>
       <c r="E21" s="80">
         <v>3.2</v>
       </c>
       <c r="F21" s="81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G21" s="83"/>
       <c r="H21" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I21" s="131"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="123"/>
       <c r="B22" s="124" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C22" s="132"/>
       <c r="D22" s="126"/>
@@ -2638,32 +2635,32 @@
         <v>3.3</v>
       </c>
       <c r="F22" s="86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G22" s="87"/>
       <c r="H22" s="87"/>
       <c r="I22" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="133"/>
       <c r="B23" s="124" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D23" s="54"/>
       <c r="E23" s="111">
         <v>3.4</v>
       </c>
       <c r="F23" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G23" s="73"/>
       <c r="H23" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I23" s="73"/>
     </row>
@@ -2671,12 +2668,12 @@
       <c r="A24" s="133"/>
       <c r="B24" s="124"/>
       <c r="C24" s="135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D24" s="126"/>
       <c r="E24" s="112"/>
       <c r="F24" s="66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" s="66"/>
       <c r="H24" s="66"/>
@@ -2691,12 +2688,12 @@
         <v>3.5</v>
       </c>
       <c r="F25" s="136" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G25" s="88"/>
       <c r="H25" s="88"/>
       <c r="I25" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2704,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="116" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C26" s="54"/>
       <c r="D26" s="137"/>
@@ -2717,20 +2714,20 @@
     <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="123"/>
       <c r="B27" s="124" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C27" s="125" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="139"/>
       <c r="E27" s="127">
         <v>4.0999999999999996</v>
       </c>
       <c r="F27" s="128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G27" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H27" s="140"/>
       <c r="I27" s="140"/>
@@ -2738,28 +2735,28 @@
     <row r="28" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="123"/>
       <c r="B28" s="124" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" s="139"/>
       <c r="E28" s="127">
         <v>4.2</v>
       </c>
       <c r="F28" s="141" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G28" s="140"/>
       <c r="H28" s="83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I28" s="140"/>
     </row>
     <row r="29" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="123"/>
       <c r="B29" s="124" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C29" s="142"/>
       <c r="D29" s="139"/>
@@ -2767,32 +2764,32 @@
         <v>4.3</v>
       </c>
       <c r="F29" s="144" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G29" s="145"/>
       <c r="H29" s="145"/>
       <c r="I29" s="146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="133"/>
       <c r="B30" s="124" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C30" s="134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="54"/>
       <c r="E30" s="111">
         <v>4.4000000000000004</v>
       </c>
       <c r="F30" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I30" s="73"/>
     </row>
@@ -2800,12 +2797,12 @@
       <c r="A31" s="133"/>
       <c r="B31" s="124"/>
       <c r="C31" s="135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31" s="126"/>
       <c r="E31" s="112"/>
       <c r="F31" s="66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G31" s="66"/>
       <c r="H31" s="66"/>
@@ -2820,12 +2817,12 @@
         <v>4.5</v>
       </c>
       <c r="F32" s="95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G32" s="146"/>
       <c r="H32" s="146"/>
       <c r="I32" s="146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2833,10 +2830,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="149" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="150" t="s">
         <v>193</v>
-      </c>
-      <c r="C33" s="150" t="s">
-        <v>194</v>
       </c>
       <c r="D33" s="151"/>
       <c r="E33" s="152"/>
@@ -2844,7 +2841,7 @@
       <c r="G33" s="153"/>
       <c r="H33" s="153"/>
       <c r="I33" s="146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -2853,13 +2850,13 @@
     <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="154"/>
       <c r="G35" s="155" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" s="155" t="s">
         <v>195</v>
       </c>
-      <c r="H35" s="155" t="s">
+      <c r="I35" s="155" t="s">
         <v>196</v>
-      </c>
-      <c r="I35" s="155" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -2879,24 +2876,24 @@
     </row>
     <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="165" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="166" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="166" t="s">
+      <c r="I39" s="167" t="s">
         <v>199</v>
-      </c>
-      <c r="I39" s="167" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="G40" s="168" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="169" t="s">
         <v>201</v>
       </c>
-      <c r="H40" s="169" t="s">
+      <c r="I40" s="170" t="s">
         <v>202</v>
-      </c>
-      <c r="I40" s="170" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2937,13 +2934,11 @@
   <sheetFormatPr defaultColWidth="13.8984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>137</v>
-      </c>
+      <c r="A1" s="2"/>
     </row>
     <row r="2" spans="1:1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
